--- a/九龙-将军澳-Grand Seasons/Grand Seasons_销控明细表.xlsx
+++ b/九龙-将军澳-Grand Seasons/Grand Seasons_销控明细表.xlsx
@@ -759,7 +759,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -22539,7 +22539,7 @@
       </c>
       <c r="F353" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G353" s="3" t="inlineStr">
@@ -22609,7 +22609,7 @@
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G354" s="3" t="inlineStr">
@@ -22679,7 +22679,7 @@
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G355" s="3" t="inlineStr">
@@ -22749,7 +22749,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -22819,7 +22819,7 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -22889,7 +22889,7 @@
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
@@ -41324,60 +41324,60 @@
           <t>66</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 443呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>B | 495呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>C | 453呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>D | 437呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>E | 323呎 (1房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
         <is>
           <t>G | 330呎 (1房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -44609,52 +44609,52 @@
           <t>66</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 716呎 (3房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>B | 457呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>C | 453呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>D | 435呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>E | 322呎 (1房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
